--- a/truck_schedule_output.xlsx
+++ b/truck_schedule_output.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="244">
   <si>
     <t>Truck1</t>
   </si>
@@ -46,691 +46,721 @@
     <t>Outsourcing</t>
   </si>
   <si>
-    <t>9, Start: 7:00, End: 7:42</t>
-  </si>
-  <si>
-    <t>wait to deliver 9, Start: 7:42, End: 14:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 14:00, End: 14:41</t>
-  </si>
-  <si>
-    <t>70, Start: 7:00, End: 7:49</t>
-  </si>
-  <si>
-    <t>wait to deliver 70, Start: 7:49, End: 12:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 12:30, End: 13:18</t>
-  </si>
-  <si>
-    <t>74, Start: 7:00, End: 7:40</t>
-  </si>
-  <si>
-    <t>wait to deliver 74, Start: 7:40, End: 10:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 10:00, End: 10:39</t>
-  </si>
-  <si>
-    <t>26, Start: 7:00, End: 8:00</t>
-  </si>
-  <si>
-    <t>wait to deliver 26, Start: 8:00, End: 8:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 8:30, End: 9:31</t>
-  </si>
-  <si>
-    <t>96, Start: 7:00, End: 7:22</t>
-  </si>
-  <si>
-    <t>wait to deliver 96, Start: 7:22, End: 16:00</t>
-  </si>
-  <si>
-    <t>51, Start: 16:00, End: 17:01</t>
-  </si>
-  <si>
-    <t>wait to deliver 51, Start: 17:01, End: 17:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:00, End: 17:59</t>
-  </si>
-  <si>
-    <t>29, Start: 7:00, End: 7:23</t>
-  </si>
-  <si>
-    <t>wait to deliver 29, Start: 7:23, End: 12:00</t>
-  </si>
-  <si>
-    <t>32, Start: 12:00, End: 12:43</t>
-  </si>
-  <si>
-    <t>wait to deliver 32, Start: 12:43, End: 14:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 14:30, End: 15:12</t>
-  </si>
-  <si>
-    <t>6, Start: 7:00, End: 7:43</t>
-  </si>
-  <si>
-    <t>wait to deliver 6, Start: 7:43, End: 13:00</t>
-  </si>
-  <si>
-    <t>80, Start: 13:00, End: 13:21</t>
-  </si>
-  <si>
-    <t>wait to deliver 80, Start: 13:21, End: 14:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 14:00, End: 14:23</t>
-  </si>
-  <si>
-    <t>17, Start: 7:00, End: 7:42</t>
-  </si>
-  <si>
-    <t>wait to deliver 17, Start: 7:42, End: 10:00</t>
-  </si>
-  <si>
-    <t>78, Start: 10:00, End: 10:36</t>
-  </si>
-  <si>
-    <t>wait to deliver 78, Start: 10:36, End: 16:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 16:30, End: 17:07</t>
-  </si>
-  <si>
-    <t>89, Start: 7:00, End: 7:40</t>
-  </si>
-  <si>
-    <t>wait to deliver 89, Start: 7:40, End: 12:00</t>
-  </si>
-  <si>
-    <t>83, Start: 12:00, End: 12:42</t>
-  </si>
-  <si>
-    <t>wait to deliver 83, Start: 12:42, End: 15:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 15:30, End: 16:09</t>
-  </si>
-  <si>
-    <t>2, Start: 7:00, End: 7:29</t>
-  </si>
-  <si>
-    <t>wait to deliver 2, Start: 7:29, End: 12:00</t>
-  </si>
-  <si>
-    <t>55, Start: 12:00, End: 12:13</t>
-  </si>
-  <si>
-    <t>wait to deliver 55, Start: 12:13, End: 15:00</t>
-  </si>
-  <si>
-    <t>61, Start: 15:00, End: 15:19</t>
-  </si>
-  <si>
-    <t>wait to deliver 61, Start: 15:19, End: 17:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:00, End: 17:19</t>
-  </si>
-  <si>
-    <t>84, Start: 7:00, End: 8:05</t>
-  </si>
-  <si>
-    <t>wait to deliver 84, Start: 8:05, End: 13:00</t>
-  </si>
-  <si>
-    <t>46, Start: 13:00, End: 14:06</t>
-  </si>
-  <si>
-    <t>wait to deliver 46, Start: 14:06, End: 15:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 15:30, End: 16:38</t>
-  </si>
-  <si>
-    <t>33, Start: 7:00, End: 8:05</t>
-  </si>
-  <si>
-    <t>wait to deliver 33, Start: 8:05, End: 9:30</t>
-  </si>
-  <si>
-    <t>49, Start: 9:30, End: 10:31</t>
-  </si>
-  <si>
-    <t>wait to deliver 49, Start: 10:31, End: 15:00</t>
-  </si>
-  <si>
-    <t>16, Start: 15:00, End: 15:34</t>
-  </si>
-  <si>
-    <t>wait to deliver 16, Start: 15:34, End: 17:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:00, End: 17:37</t>
-  </si>
-  <si>
-    <t>79, Start: 7:00, End: 7:38</t>
-  </si>
-  <si>
-    <t>wait to deliver 79, Start: 7:38, End: 17:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:00, End: 17:38</t>
-  </si>
-  <si>
-    <t>54, Start: 7:00, End: 7:48</t>
-  </si>
-  <si>
-    <t>wait to deliver 54, Start: 7:48, End: 15:00</t>
-  </si>
-  <si>
-    <t>98, Start: 15:00, End: 16:03</t>
-  </si>
-  <si>
-    <t>wait to deliver 98, Start: 16:03, End: 16:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 16:30, End: 17:34</t>
-  </si>
-  <si>
-    <t>10, Start: 7:00, End: 7:42</t>
-  </si>
-  <si>
-    <t>wait to deliver 10, Start: 7:42, End: 11:00</t>
-  </si>
-  <si>
-    <t>93, Start: 11:00, End: 11:21</t>
-  </si>
-  <si>
-    <t>wait to deliver 93, Start: 11:21, End: 12:00</t>
-  </si>
-  <si>
-    <t>94, Start: 12:00, End: 12:54</t>
-  </si>
-  <si>
-    <t>wait to deliver 94, Start: 12:54, End: 16:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 16:30, End: 17:23</t>
-  </si>
-  <si>
-    <t>52, Start: 7:00, End: 7:46</t>
-  </si>
-  <si>
-    <t>wait to deliver 52, Start: 7:46, End: 9:00</t>
-  </si>
-  <si>
-    <t>62, Start: 9:00, End: 9:58</t>
-  </si>
-  <si>
-    <t>wait to deliver 62, Start: 9:58, End: 16:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 16:00, End: 16:59</t>
-  </si>
-  <si>
-    <t>86, Start: 7:00, End: 8:04</t>
-  </si>
-  <si>
-    <t>wait to deliver 86, Start: 8:04, End: 10:30</t>
-  </si>
-  <si>
-    <t>27, Start: 10:30, End: 10:40</t>
-  </si>
-  <si>
-    <t>wait to deliver 27, Start: 10:40, End: 13:00</t>
-  </si>
-  <si>
-    <t>30, Start: 13:00, End: 14:06</t>
-  </si>
-  <si>
-    <t>wait to deliver 30, Start: 14:06, End: 16:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 16:30, End: 17:33</t>
-  </si>
-  <si>
-    <t>Order: 92</t>
-  </si>
-  <si>
-    <t>Order: 34</t>
-  </si>
-  <si>
-    <t>68, Start: 7:00, End: 7:55</t>
-  </si>
-  <si>
-    <t>wait to deliver 68, Start: 7:55, End: 10:30</t>
-  </si>
-  <si>
-    <t>58, Start: 10:30, End: 10:53</t>
-  </si>
-  <si>
-    <t>wait to deliver 58, Start: 10:53, End: 11:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 11:30, End: 11:52</t>
-  </si>
-  <si>
-    <t>41, Start: 7:00, End: 7:16</t>
-  </si>
-  <si>
-    <t>wait to deliver 41, Start: 7:16, End: 10:00</t>
-  </si>
-  <si>
-    <t>22, Start: 10:00, End: 10:54</t>
-  </si>
-  <si>
-    <t>wait to deliver 22, Start: 10:54, End: 12:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 12:00, End: 12:54</t>
-  </si>
-  <si>
-    <t>60, Start: 7:00, End: 7:17</t>
-  </si>
-  <si>
-    <t>wait to deliver 60, Start: 7:17, End: 10:00</t>
-  </si>
-  <si>
-    <t>56, Start: 10:00, End: 10:25</t>
-  </si>
-  <si>
-    <t>wait to deliver 56, Start: 10:25, End: 12:30</t>
-  </si>
-  <si>
-    <t>47, Start: 12:30, End: 13:17</t>
-  </si>
-  <si>
-    <t>wait to deliver 47, Start: 13:17, End: 14:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 14:00, End: 14:49</t>
-  </si>
-  <si>
-    <t>57, Start: 7:00, End: 7:34</t>
-  </si>
-  <si>
-    <t>wait to deliver 57, Start: 7:34, End: 8:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 8:30, End: 9:03</t>
-  </si>
-  <si>
-    <t>Order: 13</t>
+    <t>9, 13:18 - 14:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 9, 14:00 - 14:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 14:00 - 14:41</t>
+  </si>
+  <si>
+    <t>70, 11:41 - 12:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 70, 12:30 - 12:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 12:30 - 13:18</t>
+  </si>
+  <si>
+    <t>26, 7:30 - 8:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 26, 8:30 - 8:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 8:30 - 9:31</t>
+  </si>
+  <si>
+    <t>74, 9:20 - 10:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 74, 10:00 - 10:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 10:00 - 10:39</t>
+  </si>
+  <si>
+    <t>83, 14:48 - 15:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 83, 15:30 - 15:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:30 - 16:09</t>
+  </si>
+  <si>
+    <t>29, 11:37 - 12:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 29, 12:00 - 12:00</t>
+  </si>
+  <si>
+    <t>32, 12:00 - 12:43</t>
+  </si>
+  <si>
+    <t>wait to deliver 32, 12:43 - 14:30</t>
+  </si>
+  <si>
+    <t>96, 14:30 - 14:52</t>
+  </si>
+  <si>
+    <t>wait to deliver 96, 14:52 - 16:00</t>
+  </si>
+  <si>
+    <t>16, 16:00 - 16:34</t>
+  </si>
+  <si>
+    <t>wait to deliver 16, 16:34 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 17:37</t>
+  </si>
+  <si>
+    <t>33, 8:25 - 9:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 33, 9:30 - 9:30</t>
+  </si>
+  <si>
+    <t>78, 9:30 - 10:06</t>
+  </si>
+  <si>
+    <t>wait to deliver 78, 10:06 - 16:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 16:30 - 17:07</t>
+  </si>
+  <si>
+    <t>93, 11:39 - 12:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 93, 12:00 - 12:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 12:00 - 12:18</t>
+  </si>
+  <si>
+    <t>51, 15:59 - 17:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 51, 17:00 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 17:59</t>
+  </si>
+  <si>
+    <t>17, 9:18 - 10:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 17, 10:00 - 10:00</t>
+  </si>
+  <si>
+    <t>94, 10:00 - 10:54</t>
+  </si>
+  <si>
+    <t>wait to deliver 94, 10:54 - 16:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 16:30 - 17:23</t>
+  </si>
+  <si>
+    <t>6, 12:17 - 13:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 6, 13:00 - 13:00</t>
+  </si>
+  <si>
+    <t>55, 13:00 - 13:13</t>
+  </si>
+  <si>
+    <t>wait to deliver 55, 13:13 - 15:00</t>
+  </si>
+  <si>
+    <t>61, 15:00 - 15:19</t>
+  </si>
+  <si>
+    <t>wait to deliver 61, 15:19 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 17:19</t>
+  </si>
+  <si>
+    <t>89, 11:20 - 12:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 89, 12:00 - 12:00</t>
+  </si>
+  <si>
+    <t>80, 12:00 - 12:21</t>
+  </si>
+  <si>
+    <t>wait to deliver 80, 12:21 - 14:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 14:00 - 14:23</t>
+  </si>
+  <si>
+    <t>56, 12:05 - 12:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 56, 12:30 - 12:30</t>
+  </si>
+  <si>
+    <t>79, 12:30 - 13:08</t>
+  </si>
+  <si>
+    <t>wait to deliver 79, 13:08 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 17:38</t>
+  </si>
+  <si>
+    <t>85, 10:52 - 11:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 85, 11:30 - 11:30</t>
+  </si>
+  <si>
+    <t>46, 11:30 - 12:36</t>
+  </si>
+  <si>
+    <t>wait to deliver 46, 12:36 - 15:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:30 - 16:38</t>
+  </si>
+  <si>
+    <t>84, 11:55 - 13:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 84, 13:00 - 13:00</t>
+  </si>
+  <si>
+    <t>49, 13:00 - 14:01</t>
+  </si>
+  <si>
+    <t>wait to deliver 49, 14:01 - 15:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:00 - 16:01</t>
+  </si>
+  <si>
+    <t>14, 11:20 - 12:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 14, 12:00 - 12:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 12:00 - 12:45</t>
+  </si>
+  <si>
+    <t>Order: 41</t>
+  </si>
+  <si>
+    <t>86, 9:26 - 10:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 86, 10:30 - 10:30</t>
+  </si>
+  <si>
+    <t>22, 10:30 - 11:24</t>
+  </si>
+  <si>
+    <t>wait to deliver 22, 11:24 - 12:00</t>
+  </si>
+  <si>
+    <t>30, 12:00 - 13:06</t>
+  </si>
+  <si>
+    <t>wait to deliver 30, 13:06 - 16:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 16:30 - 17:33</t>
+  </si>
+  <si>
+    <t>2, 11:31 - 12:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 2, 12:00 - 12:00</t>
+  </si>
+  <si>
+    <t>54, 12:00 - 12:48</t>
+  </si>
+  <si>
+    <t>wait to deliver 54, 12:48 - 15:00</t>
+  </si>
+  <si>
+    <t>98, 15:00 - 16:03</t>
+  </si>
+  <si>
+    <t>wait to deliver 98, 16:03 - 16:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 16:30 - 17:34</t>
+  </si>
+  <si>
+    <t>52, 8:14 - 9:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 52, 9:00 - 9:00</t>
+  </si>
+  <si>
+    <t>88, 9:00 - 9:46</t>
+  </si>
+  <si>
+    <t>wait to deliver 88, 9:46 - 11:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 11:00 - 11:48</t>
+  </si>
+  <si>
+    <t>10, 10:18 - 11:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 10, 11:00 - 11:00</t>
+  </si>
+  <si>
+    <t>27, 11:00 - 11:10</t>
+  </si>
+  <si>
+    <t>wait to deliver 27, 11:10 - 13:00</t>
+  </si>
+  <si>
+    <t>62, 13:00 - 13:58</t>
+  </si>
+  <si>
+    <t>wait to deliver 62, 13:58 - 16:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>76, 10:00 - 11:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 76, 11:00 - 11:00</t>
+  </si>
+  <si>
+    <t>53, 11:00 - 12:02</t>
+  </si>
+  <si>
+    <t>wait to deliver 53, 12:02 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 18:01</t>
+  </si>
+  <si>
+    <t>60, 9:43 - 10:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 60, 10:00 - 10:00</t>
+  </si>
+  <si>
+    <t>34, 10:00 - 10:22</t>
+  </si>
+  <si>
+    <t>wait to deliver 34, 10:22 - 11:30</t>
+  </si>
+  <si>
+    <t>71, 11:30 - 12:13</t>
+  </si>
+  <si>
+    <t>wait to deliver 71, 12:13 - 13:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 13:30 - 14:13</t>
+  </si>
+  <si>
+    <t>57, 7:56 - 8:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 57, 8:30 - 8:30</t>
+  </si>
+  <si>
+    <t>8, 8:30 - 9:20</t>
+  </si>
+  <si>
+    <t>wait to deliver 8, 9:20 - 14:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 14:30 - 15:20</t>
+  </si>
+  <si>
+    <t>68, 9:35 - 10:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 68, 10:30 - 10:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 10:30 - 11:25</t>
+  </si>
+  <si>
+    <t>Order: 19</t>
+  </si>
+  <si>
+    <t>95, 8:21 - 9:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 95, 9:00 - 9:00</t>
+  </si>
+  <si>
+    <t>36, 9:00 - 9:24</t>
+  </si>
+  <si>
+    <t>wait to deliver 36, 9:24 - 11:00</t>
+  </si>
+  <si>
+    <t>64, 11:00 - 11:58</t>
+  </si>
+  <si>
+    <t>wait to deliver 64, 11:58 - 14:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 14:30 - 15:28</t>
+  </si>
+  <si>
+    <t>67, 7:03 - 8:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 67, 8:00 - 8:00</t>
+  </si>
+  <si>
+    <t>82, 8:00 - 8:10</t>
+  </si>
+  <si>
+    <t>wait to deliver 82, 8:10 - 10:00</t>
+  </si>
+  <si>
+    <t>39, 10:00 - 10:54</t>
+  </si>
+  <si>
+    <t>wait to deliver 39, 10:54 - 15:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:30 - 16:21</t>
+  </si>
+  <si>
+    <t>13, 9:36 - 10:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 13, 10:00 - 10:00</t>
+  </si>
+  <si>
+    <t>21, 10:00 - 10:37</t>
+  </si>
+  <si>
+    <t>wait to deliver 21, 10:37 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 17:28</t>
+  </si>
+  <si>
+    <t>11, 7:27 - 8:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 11, 8:30 - 8:30</t>
+  </si>
+  <si>
+    <t>91, 8:30 - 9:04</t>
+  </si>
+  <si>
+    <t>wait to deliver 91, 9:04 - 13:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 13:00 - 13:33</t>
   </si>
   <si>
     <t>Order: 81</t>
   </si>
   <si>
-    <t>Order: 88</t>
-  </si>
-  <si>
-    <t>Order: 48</t>
-  </si>
-  <si>
-    <t>11, Start: 7:00, End: 8:03</t>
-  </si>
-  <si>
-    <t>wait to deliver 11, Start: 8:03, End: 8:30</t>
-  </si>
-  <si>
-    <t>71, Start: 8:30, End: 9:13</t>
-  </si>
-  <si>
-    <t>wait to deliver 71, Start: 9:13, End: 13:30</t>
-  </si>
-  <si>
-    <t>39, Start: 13:30, End: 14:24</t>
-  </si>
-  <si>
-    <t>wait to deliver 39, Start: 14:24, End: 15:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 15:30, End: 16:21</t>
-  </si>
-  <si>
-    <t>67, Start: 7:00, End: 7:57</t>
-  </si>
-  <si>
-    <t>wait to deliver 67, Start: 7:57, End: 8:00</t>
-  </si>
-  <si>
-    <t>20, Start: 8:00, End: 8:42</t>
-  </si>
-  <si>
-    <t>wait to deliver 20, Start: 8:42, End: 11:30</t>
-  </si>
-  <si>
-    <t>64, Start: 11:30, End: 12:28</t>
-  </si>
-  <si>
-    <t>wait to deliver 64, Start: 12:28, End: 14:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 14:30, End: 15:28</t>
-  </si>
-  <si>
-    <t>44, Start: 7:00, End: 7:18</t>
-  </si>
-  <si>
-    <t>wait to deliver 44, Start: 7:18, End: 14:00</t>
-  </si>
-  <si>
-    <t>53, Start: 14:00, End: 15:02</t>
-  </si>
-  <si>
-    <t>wait to deliver 53, Start: 15:02, End: 17:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:00, End: 18:01</t>
-  </si>
-  <si>
-    <t>76, Start: 7:00, End: 8:00</t>
-  </si>
-  <si>
-    <t>wait to deliver 76, Start: 8:00, End: 11:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 11:00, End: 11:58</t>
-  </si>
-  <si>
-    <t>Order: 21</t>
-  </si>
-  <si>
-    <t>Order: 8</t>
-  </si>
-  <si>
-    <t>Order: 91</t>
-  </si>
-  <si>
-    <t>Order: 82</t>
-  </si>
-  <si>
-    <t>85, Start: 7:00, End: 7:38</t>
-  </si>
-  <si>
-    <t>wait to deliver 85, Start: 7:38, End: 11:30</t>
-  </si>
-  <si>
-    <t>59, Start: 11:30, End: 12:04</t>
-  </si>
-  <si>
-    <t>wait to deliver 59, Start: 12:04, End: 15:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 15:00, End: 15:33</t>
-  </si>
-  <si>
-    <t>14, Start: 7:00, End: 7:40</t>
-  </si>
-  <si>
-    <t>wait to deliver 14, Start: 7:40, End: 12:00</t>
-  </si>
-  <si>
-    <t>4, Start: 12:00, End: 12:45</t>
-  </si>
-  <si>
-    <t>wait to deliver 4, Start: 12:45, End: 14:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 14:00, End: 14:44</t>
-  </si>
-  <si>
-    <t>87, Start: 7:00, End: 7:38</t>
-  </si>
-  <si>
-    <t>wait to deliver 87, Start: 7:38, End: 12:30</t>
-  </si>
-  <si>
-    <t>97, Start: 12:30, End: 13:26</t>
-  </si>
-  <si>
-    <t>wait to deliver 97, Start: 13:26, End: 15:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 15:30, End: 16:24</t>
-  </si>
-  <si>
-    <t>45, Start: 7:00, End: 7:57</t>
-  </si>
-  <si>
-    <t>wait to deliver 45, Start: 7:57, End: 9:30</t>
-  </si>
-  <si>
-    <t>42, Start: 9:30, End: 9:54</t>
-  </si>
-  <si>
-    <t>wait to deliver 42, Start: 9:54, End: 14:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 14:30, End: 14:56</t>
-  </si>
-  <si>
-    <t>73, Start: 7:00, End: 7:28</t>
-  </si>
-  <si>
-    <t>wait to deliver 73, Start: 7:28, End: 12:00</t>
-  </si>
-  <si>
-    <t>31, Start: 12:00, End: 12:50</t>
-  </si>
-  <si>
-    <t>wait to deliver 31, Start: 12:50, End: 17:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:00, End: 17:48</t>
-  </si>
-  <si>
-    <t>99, Start: 7:00, End: 7:17</t>
-  </si>
-  <si>
-    <t>wait to deliver 99, Start: 7:17, End: 11:30</t>
-  </si>
-  <si>
-    <t>37, Start: 11:30, End: 12:12</t>
-  </si>
-  <si>
-    <t>wait to deliver 37, Start: 12:12, End: 15:30</t>
-  </si>
-  <si>
-    <t>18, Start: 15:30, End: 15:43</t>
-  </si>
-  <si>
-    <t>wait to deliver 18, Start: 15:43, End: 17:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:00, End: 17:13</t>
-  </si>
-  <si>
-    <t>36, Start: 7:00, End: 7:24</t>
-  </si>
-  <si>
-    <t>wait to deliver 36, Start: 7:24, End: 11:00</t>
-  </si>
-  <si>
-    <t>19, Start: 11:00, End: 11:18</t>
-  </si>
-  <si>
-    <t>wait to deliver 19, Start: 11:18, End: 17:00</t>
-  </si>
-  <si>
-    <t>65, Start: 7:00, End: 7:45</t>
-  </si>
-  <si>
-    <t>wait to deliver 65, Start: 7:45, End: 16:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 16:30, End: 17:17</t>
-  </si>
-  <si>
-    <t>Order: 24</t>
-  </si>
-  <si>
-    <t>72, Start: 7:00, End: 7:37</t>
-  </si>
-  <si>
-    <t>wait to deliver 72, Start: 7:37, End: 9:30</t>
-  </si>
-  <si>
-    <t>35, Start: 9:30, End: 10:21</t>
-  </si>
-  <si>
-    <t>wait to deliver 35, Start: 10:21, End: 11:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 11:00, End: 11:50</t>
-  </si>
-  <si>
-    <t>23, Start: 7:00, End: 7:40</t>
-  </si>
-  <si>
-    <t>wait to deliver 23, Start: 7:40, End: 14:30</t>
-  </si>
-  <si>
-    <t>75, Start: 14:30, End: 15:18</t>
-  </si>
-  <si>
-    <t>wait to deliver 75, Start: 15:18, End: 15:30</t>
-  </si>
-  <si>
-    <t>25, Start: 15:30, End: 15:55</t>
-  </si>
-  <si>
-    <t>wait to deliver 25, Start: 15:55, End: 17:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:00, End: 17:29</t>
-  </si>
-  <si>
-    <t>12, Start: 7:00, End: 7:54</t>
-  </si>
-  <si>
-    <t>wait to deliver 12, Start: 7:54, End: 9:00</t>
-  </si>
-  <si>
-    <t>3, Start: 9:00, End: 9:42</t>
-  </si>
-  <si>
-    <t>wait to deliver 3, Start: 9:42, End: 15:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 15:00, End: 15:43</t>
-  </si>
-  <si>
-    <t>95, Start: 7:00, End: 7:39</t>
-  </si>
-  <si>
-    <t>wait to deliver 95, Start: 7:39, End: 9:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 9:00, End: 9:40</t>
-  </si>
-  <si>
-    <t>38, Start: 7:00, End: 7:50</t>
-  </si>
-  <si>
-    <t>wait to deliver 38, Start: 7:50, End: 8:30</t>
-  </si>
-  <si>
-    <t>43, Start: 8:30, End: 9:09</t>
-  </si>
-  <si>
-    <t>wait to deliver 43, Start: 9:09, End: 17:00</t>
-  </si>
-  <si>
-    <t>40, Start: 7:00, End: 7:12</t>
-  </si>
-  <si>
-    <t>wait to deliver 40, Start: 7:12, End: 8:00</t>
-  </si>
-  <si>
-    <t>1, Start: 8:00, End: 8:39</t>
-  </si>
-  <si>
-    <t>wait to deliver 1, Start: 8:39, End: 10:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 10:30, End: 11:10</t>
-  </si>
-  <si>
-    <t>77, Start: 7:00, End: 7:28</t>
-  </si>
-  <si>
-    <t>wait to deliver 77, Start: 7:28, End: 10:00</t>
-  </si>
-  <si>
-    <t>5, Start: 10:00, End: 10:33</t>
-  </si>
-  <si>
-    <t>wait to deliver 5, Start: 10:33, End: 15:00</t>
-  </si>
-  <si>
-    <t>7, Start: 15:00, End: 15:48</t>
-  </si>
-  <si>
-    <t>wait to deliver 7, Start: 15:48, End: 17:00</t>
-  </si>
-  <si>
-    <t>90, Start: 7:00, End: 7:26</t>
-  </si>
-  <si>
-    <t>wait to deliver 90, Start: 7:26, End: 11:30</t>
-  </si>
-  <si>
-    <t>28, Start: 11:30, End: 12:29</t>
-  </si>
-  <si>
-    <t>wait to deliver 28, Start: 12:29, End: 17:30</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 17:30, End: 18:28</t>
-  </si>
-  <si>
-    <t>69, Start: 7:00, End: 8:00</t>
-  </si>
-  <si>
-    <t>wait to deliver 69, Start: 8:00, End: 14:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 14:00, End: 14:59</t>
-  </si>
-  <si>
-    <t>63, Start: 7:00, End: 8:01</t>
-  </si>
-  <si>
-    <t>wait to deliver 63, Start: 8:01, End: 11:30</t>
-  </si>
-  <si>
-    <t>50, Start: 11:30, End: 11:45</t>
-  </si>
-  <si>
-    <t>wait to deliver 50, Start: 11:45, End: 16:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 16:00, End: 16:17</t>
-  </si>
-  <si>
-    <t>15, Start: 7:00, End: 7:35</t>
-  </si>
-  <si>
-    <t>wait to deliver 15, Start: 7:35, End: 15:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 15:00, End: 15:31</t>
-  </si>
-  <si>
-    <t>66, Start: 7:00, End: 7:16</t>
-  </si>
-  <si>
-    <t>wait to deliver 66, Start: 7:16, End: 16:00</t>
-  </si>
-  <si>
-    <t>Go back to warehouse, Start: 16:00, End: 16:22</t>
+    <t>92, 10:37 - 11:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 92, 11:30 - 11:30</t>
+  </si>
+  <si>
+    <t>59, 11:30 - 12:04</t>
+  </si>
+  <si>
+    <t>wait to deliver 59, 12:04 - 15:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:00 - 15:33</t>
+  </si>
+  <si>
+    <t>24, 7:15 - 8:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 24, 8:00 - 8:00</t>
+  </si>
+  <si>
+    <t>45, 8:00 - 8:57</t>
+  </si>
+  <si>
+    <t>wait to deliver 45, 8:57 - 9:30</t>
+  </si>
+  <si>
+    <t>58, 9:30 - 9:53</t>
+  </si>
+  <si>
+    <t>wait to deliver 58, 9:53 - 11:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 11:30 - 11:52</t>
+  </si>
+  <si>
+    <t>12, 8:06 - 9:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 12, 9:00 - 9:00</t>
+  </si>
+  <si>
+    <t>47, 9:00 - 9:47</t>
+  </si>
+  <si>
+    <t>wait to deliver 47, 9:47 - 14:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 14:00 - 14:49</t>
+  </si>
+  <si>
+    <t>42, 14:06 - 14:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 42, 14:30 - 14:30</t>
+  </si>
+  <si>
+    <t>97, 14:30 - 15:26</t>
+  </si>
+  <si>
+    <t>wait to deliver 97, 15:26 - 15:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:30 - 16:24</t>
+  </si>
+  <si>
+    <t>Order: 44</t>
+  </si>
+  <si>
+    <t>87, 11:52 - 12:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 87, 12:30 - 12:30</t>
+  </si>
+  <si>
+    <t>18, 12:30 - 12:43</t>
+  </si>
+  <si>
+    <t>wait to deliver 18, 12:43 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 17:13</t>
+  </si>
+  <si>
+    <t>20, 10:48 - 11:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 20, 11:30 - 11:30</t>
+  </si>
+  <si>
+    <t>4, 11:30 - 12:15</t>
+  </si>
+  <si>
+    <t>wait to deliver 4, 12:15 - 14:00</t>
+  </si>
+  <si>
+    <t>37, 14:00 - 14:42</t>
+  </si>
+  <si>
+    <t>wait to deliver 37, 14:42 - 15:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:30 - 16:13</t>
+  </si>
+  <si>
+    <t>65, 15:45 - 16:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 65, 16:30 - 16:30</t>
+  </si>
+  <si>
+    <t>48, 16:30 - 16:58</t>
+  </si>
+  <si>
+    <t>wait to deliver 48, 16:58 - 17:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:30 - 17:59</t>
+  </si>
+  <si>
+    <t>35, 10:09 - 11:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 35, 11:00 - 11:00</t>
+  </si>
+  <si>
+    <t>23, 11:00 - 11:40</t>
+  </si>
+  <si>
+    <t>wait to deliver 23, 11:40 - 14:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 14:30 - 15:10</t>
+  </si>
+  <si>
+    <t>77, 9:32 - 10:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 77, 10:00 - 10:00</t>
+  </si>
+  <si>
+    <t>5, 10:00 - 10:33</t>
+  </si>
+  <si>
+    <t>wait to deliver 5, 10:33 - 15:00</t>
+  </si>
+  <si>
+    <t>25, 15:00 - 15:25</t>
+  </si>
+  <si>
+    <t>wait to deliver 25, 15:25 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 17:29</t>
+  </si>
+  <si>
+    <t>38, 7:40 - 8:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 38, 8:30 - 8:30</t>
+  </si>
+  <si>
+    <t>3, 8:30 - 9:12</t>
+  </si>
+  <si>
+    <t>wait to deliver 3, 9:12 - 15:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:00 - 15:43</t>
+  </si>
+  <si>
+    <t>75, 14:42 - 15:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 75, 15:30 - 15:30</t>
+  </si>
+  <si>
+    <t>31, 15:30 - 16:20</t>
+  </si>
+  <si>
+    <t>wait to deliver 31, 16:20 - 17:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:00 - 17:48</t>
+  </si>
+  <si>
+    <t>72, 8:53 - 9:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 72, 9:30 - 9:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 9:30 - 10:09</t>
+  </si>
+  <si>
+    <t>Order: 73</t>
+  </si>
+  <si>
+    <t>7, 16:12 - 17:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 7, 17:00 - 17:00</t>
+  </si>
+  <si>
+    <t>99, 11:13 - 11:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 99, 11:30 - 11:30</t>
+  </si>
+  <si>
+    <t>50, 11:30 - 11:45</t>
+  </si>
+  <si>
+    <t>wait to deliver 50, 11:45 - 16:00</t>
+  </si>
+  <si>
+    <t>28, 16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>wait to deliver 28, 16:59 - 17:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 17:30 - 18:28</t>
+  </si>
+  <si>
+    <t>1, 9:51 - 10:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 1, 10:30 - 10:30</t>
+  </si>
+  <si>
+    <t>90, 10:30 - 10:56</t>
+  </si>
+  <si>
+    <t>wait to deliver 90, 10:56 - 11:30</t>
+  </si>
+  <si>
+    <t>40, 7:48 - 8:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 40, 8:00 - 8:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 8:00 - 8:15</t>
+  </si>
+  <si>
+    <t>69, 13:00 - 14:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 69, 14:00 - 14:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 14:00 - 14:59</t>
+  </si>
+  <si>
+    <t>15, 14:25 - 15:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 15, 15:00 - 15:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 15:00 - 15:31</t>
+  </si>
+  <si>
+    <t>43, 16:21 - 17:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 43, 17:00 - 17:00</t>
+  </si>
+  <si>
+    <t>63, 10:29 - 11:30</t>
+  </si>
+  <si>
+    <t>wait to deliver 63, 11:30 - 11:30</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 11:30 - 12:33</t>
+  </si>
+  <si>
+    <t>66, 15:44 - 16:00</t>
+  </si>
+  <si>
+    <t>wait to deliver 66, 16:00 - 16:00</t>
+  </si>
+  <si>
+    <t>Go back to warehouse, 16:00 - 16:22</t>
   </si>
 </sst>
 </file>
@@ -1109,17 +1139,17 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1152,79 +1182,82 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>186</v>
+      </c>
+      <c r="D5" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>187</v>
+      </c>
+      <c r="D6" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -1256,76 +1289,79 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>210</v>
+      </c>
+      <c r="E2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D3" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" t="s">
-        <v>190</v>
+      <c r="A7" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="B8" t="s">
-        <v>191</v>
+      <c r="A8" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -1357,82 +1393,70 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="C2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C3" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="D4" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>203</v>
-      </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D6" t="s">
-        <v>219</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="C7" t="s">
-        <v>214</v>
+      <c r="B7" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="C8" t="s">
-        <v>164</v>
+      <c r="B8" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -1442,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1463,46 +1487,36 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>220</v>
-      </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>233</v>
+      </c>
+      <c r="D2" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>221</v>
-      </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>234</v>
+      </c>
+      <c r="D3" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>222</v>
-      </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6" t="s">
-        <v>227</v>
+        <v>235</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1511,6 +1525,48 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1519,7 +1575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1542,30 +1598,21 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="D2" t="s">
-        <v>231</v>
+      <c r="A2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="D3" t="s">
-        <v>232</v>
+      <c r="A3" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="D4" t="s">
-        <v>233</v>
+      <c r="A4" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1593,7 +1640,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="B2" t="s">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
@@ -1604,7 +1651,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="B3" t="s">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
@@ -1615,7 +1662,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="B4" t="s">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
@@ -1632,7 +1679,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1653,43 +1700,81 @@
       </c>
     </row>
     <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1721,82 +1806,76 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="D7" t="s">
-        <v>47</v>
+      <c r="C7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="D8" t="s">
-        <v>48</v>
+      <c r="C8" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1806,7 +1885,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1828,61 +1907,69 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1914,94 +2001,94 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2033,88 +2120,79 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="C7" t="s">
-        <v>105</v>
+      <c r="B7" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="C8" t="s">
-        <v>106</v>
+      <c r="B8" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2146,94 +2224,91 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="D5" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>141</v>
+      </c>
+      <c r="D6" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2243,7 +2318,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2265,71 +2340,84 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>165</v>
+      </c>
+      <c r="E2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" t="s">
         <v>159</v>
       </c>
     </row>

--- a/truck_schedule_output.xlsx
+++ b/truck_schedule_output.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\GeneticAlgorithmTruckLife\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D23381-5BBE-4AA1-9BCB-9C0B2E6BD345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20240201" sheetId="1" r:id="rId1"/>
@@ -24,7 +30,7 @@
     <sheet name="20240215" sheetId="15" r:id="rId15"/>
     <sheet name="20240216" sheetId="16" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -736,8 +742,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -800,13 +806,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -844,7 +858,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -878,6 +892,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -912,9 +927,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1087,11 +1103,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1108,17 +1124,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>7</v>
       </c>
@@ -1129,11 +1145,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1150,7 +1166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>160</v>
       </c>
@@ -1167,7 +1183,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>161</v>
       </c>
@@ -1181,7 +1197,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>162</v>
       </c>
@@ -1195,7 +1211,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>163</v>
       </c>
@@ -1206,7 +1222,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>164</v>
       </c>
@@ -1217,12 +1233,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>171</v>
       </c>
@@ -1233,11 +1249,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1254,7 +1270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>180</v>
       </c>
@@ -1268,7 +1284,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>181</v>
       </c>
@@ -1282,7 +1298,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -1296,7 +1312,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>183</v>
       </c>
@@ -1307,7 +1323,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>184</v>
       </c>
@@ -1318,12 +1334,12 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>191</v>
       </c>
@@ -1334,11 +1350,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1355,7 +1371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>200</v>
       </c>
@@ -1369,7 +1385,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>201</v>
       </c>
@@ -1383,7 +1399,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>202</v>
       </c>
@@ -1397,7 +1413,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>203</v>
       </c>
@@ -1411,7 +1427,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -1425,12 +1441,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>164</v>
       </c>
@@ -1441,11 +1457,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1462,7 +1478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>220</v>
       </c>
@@ -1473,7 +1489,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>221</v>
       </c>
@@ -1484,7 +1500,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>222</v>
       </c>
@@ -1495,12 +1511,12 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>227</v>
       </c>
@@ -1511,20 +1527,20 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1541,17 +1557,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>233</v>
       </c>
@@ -1562,20 +1578,20 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1592,7 +1608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -1603,7 +1619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -1614,7 +1630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>10</v>
       </c>
@@ -1631,11 +1647,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1652,7 +1668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>17</v>
       </c>
@@ -1660,7 +1676,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>18</v>
       </c>
@@ -1668,7 +1684,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1676,7 +1692,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -1684,7 +1700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>21</v>
       </c>
@@ -1698,11 +1714,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1719,7 +1735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1733,7 +1749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1747,7 +1763,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1761,7 +1777,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1775,7 +1791,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1789,12 +1805,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>48</v>
       </c>
@@ -1805,11 +1821,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1826,7 +1842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -1837,7 +1853,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -1848,7 +1864,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -1859,7 +1875,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -1867,7 +1883,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -1875,12 +1891,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>60</v>
       </c>
@@ -1891,11 +1907,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1912,7 +1928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1929,7 +1945,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -1946,7 +1962,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -1960,7 +1976,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -1974,7 +1990,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -1988,7 +2004,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>74</v>
       </c>
@@ -1996,7 +2012,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>75</v>
       </c>
@@ -2010,11 +2026,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2031,7 +2047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -2048,7 +2064,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -2065,7 +2081,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -2082,7 +2098,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -2096,7 +2112,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -2107,12 +2123,12 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>106</v>
       </c>
@@ -2123,11 +2139,15 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2144,7 +2164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2161,7 +2181,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>115</v>
       </c>
@@ -2178,7 +2198,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -2195,7 +2215,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>117</v>
       </c>
@@ -2209,7 +2229,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -2220,7 +2240,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -2228,7 +2248,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -2242,11 +2262,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2263,7 +2287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>140</v>
       </c>
@@ -2277,7 +2301,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>141</v>
       </c>
@@ -2291,7 +2315,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -2305,7 +2329,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>143</v>
       </c>
@@ -2319,7 +2343,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>144</v>
       </c>

--- a/truck_schedule_output.xlsx
+++ b/truck_schedule_output.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Documents\GitHub\GeneticAlgorithmTruckLife\GeneticAlgorithmTruckLife\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EB9734-FFD8-45FC-887A-87488F24E8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20241001" sheetId="1" r:id="rId1"/>
@@ -17,7 +23,7 @@
     <sheet name="20241008" sheetId="8" r:id="rId8"/>
     <sheet name="20241009" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -4179,8 +4185,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4243,13 +4249,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4287,7 +4301,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4321,6 +4335,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4355,9 +4370,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4530,11 +4546,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="10" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4569,7 +4589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4604,7 +4624,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4639,7 +4659,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -4674,7 +4694,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -4709,7 +4729,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4744,7 +4764,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4779,7 +4799,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -4814,7 +4834,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4846,7 +4866,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -4878,7 +4898,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -4907,7 +4927,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -4927,7 +4947,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -4944,7 +4964,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -4961,7 +4981,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -4972,7 +4992,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
         <v>72</v>
       </c>
@@ -4980,7 +5000,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="5:10">
+    <row r="17" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
         <v>73</v>
       </c>
@@ -4988,17 +5008,17 @@
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="5:10">
+    <row r="18" spans="5:10" x14ac:dyDescent="0.25">
       <c r="J18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="5:10">
+    <row r="19" spans="5:10" x14ac:dyDescent="0.25">
       <c r="J19" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="5:10">
+    <row r="20" spans="5:10" x14ac:dyDescent="0.25">
       <c r="J20" t="s">
         <v>135</v>
       </c>
@@ -5009,11 +5029,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5048,7 +5068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>143</v>
       </c>
@@ -5083,7 +5103,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -5118,7 +5138,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -5153,7 +5173,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -5188,7 +5208,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>147</v>
       </c>
@@ -5223,7 +5243,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -5258,7 +5278,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -5290,7 +5310,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -5322,7 +5342,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -5354,7 +5374,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -5383,7 +5403,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -5412,7 +5432,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -5435,7 +5455,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>155</v>
       </c>
@@ -5458,7 +5478,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>169</v>
       </c>
@@ -5478,7 +5498,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>170</v>
       </c>
@@ -5498,7 +5518,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>171</v>
       </c>
@@ -5518,7 +5538,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="18" spans="2:11">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>172</v>
       </c>
@@ -5538,7 +5558,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>227</v>
       </c>
@@ -5546,12 +5566,12 @@
         <v>296</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="K20" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="21" spans="2:11">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="K21" t="s">
         <v>298</v>
       </c>
@@ -5562,11 +5582,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5601,7 +5621,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>299</v>
       </c>
@@ -5636,7 +5656,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>300</v>
       </c>
@@ -5671,7 +5691,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>301</v>
       </c>
@@ -5706,7 +5726,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>302</v>
       </c>
@@ -5741,7 +5761,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>303</v>
       </c>
@@ -5776,7 +5796,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>304</v>
       </c>
@@ -5811,7 +5831,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>305</v>
       </c>
@@ -5846,7 +5866,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>306</v>
       </c>
@@ -5881,7 +5901,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>307</v>
       </c>
@@ -5916,7 +5936,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>317</v>
       </c>
@@ -5948,7 +5968,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>318</v>
       </c>
@@ -5980,7 +6000,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>330</v>
       </c>
@@ -6006,7 +6026,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>331</v>
       </c>
@@ -6029,7 +6049,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>332</v>
       </c>
@@ -6052,7 +6072,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G16" t="s">
         <v>386</v>
       </c>
@@ -6066,7 +6086,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" spans="7:11">
+    <row r="17" spans="7:11" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
         <v>387</v>
       </c>
@@ -6080,7 +6100,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="18" spans="7:11">
+    <row r="18" spans="7:11" x14ac:dyDescent="0.25">
       <c r="G18" t="s">
         <v>388</v>
       </c>
@@ -6094,7 +6114,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="19" spans="7:11">
+    <row r="19" spans="7:11" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>389</v>
       </c>
@@ -6108,7 +6128,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="20" spans="7:11">
+    <row r="20" spans="7:11" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
         <v>390</v>
       </c>
@@ -6122,7 +6142,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="21" spans="7:11">
+    <row r="21" spans="7:11" x14ac:dyDescent="0.25">
       <c r="H21" t="s">
         <v>410</v>
       </c>
@@ -6130,7 +6150,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="22" spans="7:11">
+    <row r="22" spans="7:11" x14ac:dyDescent="0.25">
       <c r="H22" t="s">
         <v>411</v>
       </c>
@@ -6138,7 +6158,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="23" spans="7:11">
+    <row r="23" spans="7:11" x14ac:dyDescent="0.25">
       <c r="H23" t="s">
         <v>412</v>
       </c>
@@ -6146,7 +6166,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="24" spans="7:11">
+    <row r="24" spans="7:11" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
         <v>413</v>
       </c>
@@ -6154,7 +6174,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="25" spans="7:11">
+    <row r="25" spans="7:11" x14ac:dyDescent="0.25">
       <c r="H25" t="s">
         <v>414</v>
       </c>
@@ -6162,32 +6182,32 @@
         <v>469</v>
       </c>
     </row>
-    <row r="26" spans="7:11">
+    <row r="26" spans="7:11" x14ac:dyDescent="0.25">
       <c r="K26" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="27" spans="7:11">
+    <row r="27" spans="7:11" x14ac:dyDescent="0.25">
       <c r="K27" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="28" spans="7:11">
+    <row r="28" spans="7:11" x14ac:dyDescent="0.25">
       <c r="K28" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="29" spans="7:11">
+    <row r="29" spans="7:11" x14ac:dyDescent="0.25">
       <c r="K29" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="30" spans="7:11">
+    <row r="30" spans="7:11" x14ac:dyDescent="0.25">
       <c r="K30" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="31" spans="7:11">
+    <row r="31" spans="7:11" x14ac:dyDescent="0.25">
       <c r="K31" t="s">
         <v>475</v>
       </c>
@@ -6198,11 +6218,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6237,7 +6257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>476</v>
       </c>
@@ -6272,7 +6292,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>477</v>
       </c>
@@ -6307,7 +6327,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>478</v>
       </c>
@@ -6342,7 +6362,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>479</v>
       </c>
@@ -6377,7 +6397,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>480</v>
       </c>
@@ -6412,7 +6432,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>481</v>
       </c>
@@ -6447,7 +6467,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>482</v>
       </c>
@@ -6482,7 +6502,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>483</v>
       </c>
@@ -6517,7 +6537,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>484</v>
       </c>
@@ -6552,7 +6572,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>485</v>
       </c>
@@ -6587,7 +6607,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>486</v>
       </c>
@@ -6619,7 +6639,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>498</v>
       </c>
@@ -6648,7 +6668,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>499</v>
       </c>
@@ -6677,7 +6697,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>513</v>
       </c>
@@ -6703,7 +6723,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>528</v>
       </c>
@@ -6726,7 +6746,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="17" spans="4:11">
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>529</v>
       </c>
@@ -6749,7 +6769,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="18" spans="4:11">
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
         <v>530</v>
       </c>
@@ -6772,7 +6792,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="19" spans="4:11">
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E19" t="s">
         <v>548</v>
       </c>
@@ -6792,7 +6812,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="20" spans="4:11">
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E20" t="s">
         <v>549</v>
       </c>
@@ -6809,7 +6829,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="21" spans="4:11">
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E21" t="s">
         <v>550</v>
       </c>
@@ -6826,37 +6846,37 @@
         <v>656</v>
       </c>
     </row>
-    <row r="22" spans="4:11">
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
       <c r="K22" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="23" spans="4:11">
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
       <c r="K23" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="24" spans="4:11">
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
       <c r="K24" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="25" spans="4:11">
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
       <c r="K25" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="26" spans="4:11">
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
       <c r="K26" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="27" spans="4:11">
+    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
       <c r="K27" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="28" spans="4:11">
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
       <c r="K28" t="s">
         <v>663</v>
       </c>
@@ -6867,11 +6887,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6906,7 +6926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>664</v>
       </c>
@@ -6941,7 +6961,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>665</v>
       </c>
@@ -6976,7 +6996,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>666</v>
       </c>
@@ -7011,7 +7031,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>667</v>
       </c>
@@ -7046,7 +7066,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>668</v>
       </c>
@@ -7081,7 +7101,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>669</v>
       </c>
@@ -7116,7 +7136,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>670</v>
       </c>
@@ -7151,7 +7171,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>671</v>
       </c>
@@ -7186,7 +7206,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>672</v>
       </c>
@@ -7218,7 +7238,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>673</v>
       </c>
@@ -7250,7 +7270,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>674</v>
       </c>
@@ -7282,7 +7302,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>675</v>
       </c>
@@ -7308,7 +7328,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>676</v>
       </c>
@@ -7331,7 +7351,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>677</v>
       </c>
@@ -7351,7 +7371,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>678</v>
       </c>
@@ -7371,7 +7391,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>679</v>
       </c>
@@ -7385,7 +7405,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>680</v>
       </c>
@@ -7399,7 +7419,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>681</v>
       </c>
@@ -7410,7 +7430,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>682</v>
       </c>
@@ -7421,7 +7441,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>683</v>
       </c>
@@ -7432,7 +7452,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>684</v>
       </c>
@@ -7440,12 +7460,12 @@
         <v>826</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K23" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K24" t="s">
         <v>828</v>
       </c>
@@ -7456,11 +7476,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7495,7 +7515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>829</v>
       </c>
@@ -7530,7 +7550,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>830</v>
       </c>
@@ -7565,7 +7585,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>831</v>
       </c>
@@ -7600,7 +7620,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>832</v>
       </c>
@@ -7635,7 +7655,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>833</v>
       </c>
@@ -7670,7 +7690,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>834</v>
       </c>
@@ -7705,7 +7725,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>835</v>
       </c>
@@ -7740,7 +7760,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>836</v>
       </c>
@@ -7775,7 +7795,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>837</v>
       </c>
@@ -7807,7 +7827,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>838</v>
       </c>
@@ -7839,7 +7859,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>839</v>
       </c>
@@ -7865,7 +7885,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>840</v>
       </c>
@@ -7891,7 +7911,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>841</v>
       </c>
@@ -7917,7 +7937,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>842</v>
       </c>
@@ -7940,7 +7960,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>843</v>
       </c>
@@ -7963,7 +7983,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="17" spans="3:11">
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>867</v>
       </c>
@@ -7977,7 +7997,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="18" spans="3:11">
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
       <c r="G18" t="s">
         <v>921</v>
       </c>
@@ -7988,17 +8008,17 @@
         <v>983</v>
       </c>
     </row>
-    <row r="19" spans="3:11">
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="20" spans="3:11">
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="21" spans="3:11">
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
       <c r="G21" t="s">
         <v>924</v>
       </c>
@@ -8009,11 +8029,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8048,7 +8068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>984</v>
       </c>
@@ -8083,7 +8103,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>985</v>
       </c>
@@ -8118,7 +8138,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>986</v>
       </c>
@@ -8153,7 +8173,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>987</v>
       </c>
@@ -8188,7 +8208,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>988</v>
       </c>
@@ -8220,7 +8240,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>989</v>
       </c>
@@ -8252,7 +8272,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>990</v>
       </c>
@@ -8284,7 +8304,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>991</v>
       </c>
@@ -8316,7 +8336,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>992</v>
       </c>
@@ -8348,7 +8368,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>993</v>
       </c>
@@ -8380,7 +8400,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>994</v>
       </c>
@@ -8412,7 +8432,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>995</v>
       </c>
@@ -8438,7 +8458,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>996</v>
       </c>
@@ -8464,7 +8484,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>997</v>
       </c>
@@ -8487,7 +8507,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>998</v>
       </c>
@@ -8507,7 +8527,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="17" spans="8:9">
+    <row r="17" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H17" t="s">
         <v>1091</v>
       </c>
@@ -8515,7 +8535,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="18" spans="8:9">
+    <row r="18" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
         <v>1092</v>
       </c>
@@ -8529,11 +8549,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8568,7 +8588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1129</v>
       </c>
@@ -8603,7 +8623,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1130</v>
       </c>
@@ -8638,7 +8658,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1131</v>
       </c>
@@ -8673,7 +8693,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1132</v>
       </c>
@@ -8708,7 +8728,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1133</v>
       </c>
@@ -8743,7 +8763,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1134</v>
       </c>
@@ -8778,7 +8798,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1135</v>
       </c>
@@ -8813,7 +8833,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1136</v>
       </c>
@@ -8845,7 +8865,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1137</v>
       </c>
@@ -8877,7 +8897,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1138</v>
       </c>
@@ -8909,7 +8929,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1139</v>
       </c>
@@ -8941,7 +8961,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1140</v>
       </c>
@@ -8970,7 +8990,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1141</v>
       </c>
@@ -8993,7 +9013,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>1178</v>
       </c>
@@ -9013,7 +9033,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>1179</v>
       </c>
@@ -9030,7 +9050,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="17" spans="4:9">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>1180</v>
       </c>
@@ -9047,7 +9067,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="18" spans="4:9">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
         <v>1197</v>
       </c>
@@ -9061,7 +9081,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="19" spans="4:9">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>1229</v>
       </c>
@@ -9069,7 +9089,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="20" spans="4:9">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
         <v>1230</v>
       </c>
@@ -9083,11 +9103,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9122,7 +9142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1285</v>
       </c>
@@ -9154,7 +9174,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1286</v>
       </c>
@@ -9186,7 +9206,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1287</v>
       </c>
@@ -9218,7 +9238,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1288</v>
       </c>
@@ -9250,7 +9270,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1289</v>
       </c>
@@ -9282,7 +9302,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1290</v>
       </c>
@@ -9314,7 +9334,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1291</v>
       </c>
@@ -9343,7 +9363,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1292</v>
       </c>
@@ -9366,7 +9386,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1293</v>
       </c>
@@ -9389,7 +9409,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>1303</v>
       </c>
@@ -9406,7 +9426,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>1304</v>
       </c>
@@ -9423,7 +9443,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
         <v>1349</v>
       </c>
@@ -9434,7 +9454,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
         <v>1350</v>
       </c>
@@ -9442,7 +9462,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G15" t="s">
         <v>1351</v>
       </c>
